--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED25.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED25.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>180W</t>
+          <t>194W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0135</t>
+          <t>SIM_XA_FIXED-2-0087</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>93W</t>
+          <t>55W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5季</t>
+          <t>4季</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>2季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,14 +1748,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第2年4季</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-3-0066</t>
+          <t>SIM_XA_FIXED-3-0017</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>143W</t>
+          <t>165W</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>5季</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2季</t>
+          <t>3季</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年1季</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G57"/>
+  <dimension ref="B2:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2189,14 +2189,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Auction_Win</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-10</v>
+        <v>-24</v>
       </c>
       <c r="E16" t="n">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>auction_bid_fee | {"order_id": "SIM_XA_FIXED-2-0165"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2215,14 +2215,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="E17" t="n">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-977548bbd8", "line_id": "L-3e5798b520", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2248,11 +2248,11 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>第2年3季</t>
+          <t>第2年2季</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2267,23 +2267,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-36</v>
+        <v>-14</v>
       </c>
       <c r="E19" t="n">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第2年3季</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2293,14 +2293,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-6db893e151", "line_id": "L-3e5798b520", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-2-0087", "receivable_term_quarters": 2, "revenue_wan": 55.0}</t>
         </is>
       </c>
     </row>
@@ -2319,14 +2319,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="E21" t="n">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2345,14 +2345,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="E22" t="n">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-3e5798b520"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-6db893e151", "line_id": "L-3e5798b520", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2371,14 +2371,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E23" t="n">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-3e5798b520", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2397,14 +2397,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E24" t="n">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-3e5798b520", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-3e5798b520"}</t>
         </is>
       </c>
     </row>
@@ -2423,23 +2423,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-3e5798b520", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2449,23 +2449,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-3e5798b520", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2475,23 +2475,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E27" t="n">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-2-0135", "receivable_term_quarters": 4, "revenue_wan": 93.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2501,23 +2501,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-36</v>
+        <v>-14</v>
       </c>
       <c r="E28" t="n">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2527,23 +2527,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-24</v>
+        <v>55</v>
       </c>
       <c r="E29" t="n">
-        <v>253</v>
+        <v>358</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-612aa8986d", "line_id": "L-3e5798b520", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
+          <t>receivable_collected | {"receivable_id": "AR-fc19e3ecd7"}</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
         <v>-14</v>
       </c>
       <c r="E30" t="n">
-        <v>239</v>
+        <v>344</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2579,14 +2579,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="E31" t="n">
-        <v>225</v>
+        <v>320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2605,23 +2605,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="E32" t="n">
-        <v>211</v>
+        <v>304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-f3ac1e41c8", "line_id": "L-3e5798b520", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2631,23 +2631,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E33" t="n">
-        <v>196</v>
+        <v>290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-3e5798b520"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E34" t="n">
-        <v>196</v>
+        <v>276</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-3e5798b520", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2683,14 +2683,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E35" t="n">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-3e5798b520", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-3e5798b520"}</t>
         </is>
       </c>
     </row>
@@ -2709,23 +2709,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>184</v>
+        <v>261</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-3e5798b520", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2735,23 +2735,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>176</v>
+        <v>261</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-2ef2042796", "line_id": "L-3e5798b520", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-3e5798b520", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2761,14 +2761,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>164</v>
+        <v>261</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-3-0017", "receivable_term_quarters": 3, "revenue_wan": 165.0}</t>
         </is>
       </c>
     </row>
@@ -2787,14 +2787,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-14</v>
+        <v>-48</v>
       </c>
       <c r="E39" t="n">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2813,14 +2813,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>93</v>
+        <v>-32</v>
       </c>
       <c r="E40" t="n">
-        <v>243</v>
+        <v>181</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-1c2a1310ee"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-2ef2042796", "line_id": "L-3e5798b520", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2839,23 +2839,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E41" t="n">
-        <v>229</v>
+        <v>169</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2865,23 +2865,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E42" t="n">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-3-0066", "receivable_term_quarters": 2, "revenue_wan": 143.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2891,23 +2891,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-48</v>
+        <v>-14</v>
       </c>
       <c r="E43" t="n">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2917,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-32</v>
+        <v>-14</v>
       </c>
       <c r="E44" t="n">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-908bce5085", "line_id": "L-3e5798b520", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2943,14 +2943,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-14</v>
+        <v>165</v>
       </c>
       <c r="E45" t="n">
-        <v>135</v>
+        <v>292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-c8a086c5bb"}</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
         <v>-14</v>
       </c>
       <c r="E46" t="n">
-        <v>121</v>
+        <v>278</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2995,14 +2995,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>143</v>
+        <v>-15</v>
       </c>
       <c r="E47" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-74ba50ab44"}</t>
+          <t>maintenance_expense | {"line_id": "L-3e5798b520"}</t>
         </is>
       </c>
     </row>
@@ -3021,14 +3021,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-3e5798b520"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-3e5798b520", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-3e5798b520", "asset_type": "factory"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-3e5798b520", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -3073,23 +3073,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E50" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-3e5798b520", "asset_type": "production_line"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -3099,11 +3099,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E51" t="n">
         <v>237</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3177,23 +3177,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E54" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-3e5798b520"}</t>
         </is>
       </c>
     </row>
@@ -3203,14 +3203,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-3e5798b520"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-3e5798b520", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3244,32 +3244,6 @@
         </is>
       </c>
       <c r="G56" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-3e5798b520", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="n">
-        <v>54</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
-        <v>180</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-3e5798b520", "asset_type": "production_line"}</t>
         </is>
@@ -3663,13 +3637,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3688,10 +3662,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>80</v>
@@ -3713,13 +3687,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3763,13 +3737,13 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
+        <v>-68</v>
+      </c>
+      <c r="F20" t="n">
         <v>-83</v>
       </c>
-      <c r="F20" t="n">
-        <v>-50</v>
-      </c>
       <c r="G20" t="n">
-        <v>-20</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>-69</v>
@@ -3813,13 +3787,13 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
+        <v>-83.2</v>
+      </c>
+      <c r="F22" t="n">
         <v>-98.2</v>
       </c>
-      <c r="F22" t="n">
-        <v>-65.2</v>
-      </c>
       <c r="G22" t="n">
-        <v>-35.2</v>
+        <v>-13.2</v>
       </c>
       <c r="H22" t="n">
         <v>-84.2</v>
@@ -3863,13 +3837,13 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-108.2</v>
+        <v>-83.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-65.2</v>
+        <v>-98.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-35.2</v>
+        <v>-13.2</v>
       </c>
       <c r="H24" t="n">
         <v>-84.2</v>
@@ -3913,13 +3887,13 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-108.2</v>
+        <v>-83.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-65.2</v>
+        <v>-98.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-35.2</v>
+        <v>-13.2</v>
       </c>
       <c r="H26" t="n">
         <v>-84.2</v>
@@ -4012,16 +3986,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="F30" t="n">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="G30" t="n">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="H30" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31">
@@ -4037,10 +4011,10 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F31" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -4062,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -4090,7 +4064,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="G33" t="n">
         <v>80</v>
@@ -4137,16 +4111,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="F35" t="n">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="G35" t="n">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="H35" t="n">
-        <v>260</v>
+        <v>274</v>
       </c>
     </row>
     <row r="36">
@@ -4262,16 +4236,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>480.6</v>
+        <v>505.6</v>
       </c>
       <c r="F40" t="n">
-        <v>415.4</v>
+        <v>407.4</v>
       </c>
       <c r="G40" t="n">
-        <v>380.2</v>
+        <v>394.2</v>
       </c>
       <c r="H40" t="n">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41">
@@ -4437,16 +4411,16 @@
         <v>-4.263256414560601e-14</v>
       </c>
       <c r="E47" t="n">
-        <v>-86.20000000000003</v>
+        <v>-86.20000000000009</v>
       </c>
       <c r="F47" t="n">
-        <v>-194.4</v>
+        <v>-169.4000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>-259.6</v>
+        <v>-267.6000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>-294.8</v>
+        <v>-280.8000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -4462,13 +4436,13 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-108.2</v>
+        <v>-83.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-65.2</v>
+        <v>-98.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-35.2</v>
+        <v>-13.2</v>
       </c>
       <c r="H48" t="n">
         <v>-84.2</v>
@@ -4487,16 +4461,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>480.6</v>
+        <v>505.5999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>415.4</v>
+        <v>407.3999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>380.2</v>
+        <v>394.1999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>296</v>
+        <v>309.9999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4512,16 +4486,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>480.6</v>
+        <v>505.5999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>415.4</v>
+        <v>407.3999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>380.2</v>
+        <v>394.1999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>296</v>
+        <v>309.9999999999999</v>
       </c>
     </row>
   </sheetData>
